--- a/research/traditional_assets/database/data/croatia/croatia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0277</v>
+        <v>0.026</v>
       </c>
       <c r="E2">
-        <v>0.128</v>
+        <v>0.119</v>
       </c>
       <c r="G2">
-        <v>0.09964349376114082</v>
+        <v>0.1363073110285006</v>
       </c>
       <c r="H2">
-        <v>0.09964349376114082</v>
+        <v>0.1363073110285006</v>
       </c>
       <c r="I2">
-        <v>0.1119429590017825</v>
+        <v>0.09376290788930194</v>
       </c>
       <c r="J2">
-        <v>0.09457546459443993</v>
+        <v>0.0783719490195993</v>
       </c>
       <c r="K2">
-        <v>55</v>
+        <v>47.5</v>
       </c>
       <c r="L2">
-        <v>0.09803921568627451</v>
+        <v>0.09809995869475424</v>
       </c>
       <c r="M2">
-        <v>0.324</v>
+        <v>0.142</v>
       </c>
       <c r="N2">
-        <v>0.0007295654131952262</v>
+        <v>0.0003616912888436067</v>
       </c>
       <c r="O2">
-        <v>0.005890909090909091</v>
+        <v>0.002989473684210526</v>
       </c>
       <c r="P2">
-        <v>0.324</v>
+        <v>0.142</v>
       </c>
       <c r="Q2">
-        <v>0.0007295654131952262</v>
+        <v>0.0003616912888436067</v>
       </c>
       <c r="R2">
-        <v>0.005890909090909091</v>
+        <v>0.002989473684210526</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>125.2</v>
+        <v>61.3</v>
       </c>
       <c r="V2">
-        <v>0.2819184868272911</v>
+        <v>0.1561385634233316</v>
       </c>
       <c r="W2">
-        <v>0.08853831294269156</v>
+        <v>0.06741413567981834</v>
       </c>
       <c r="X2">
-        <v>0.06656083271809668</v>
+        <v>0.1001974742983223</v>
       </c>
       <c r="Y2">
-        <v>0.02197748022459488</v>
+        <v>-0.03278333861850391</v>
       </c>
       <c r="Z2">
-        <v>0.9773519163763066</v>
+        <v>0.7592912027599186</v>
       </c>
       <c r="AA2">
-        <v>0.09243351156355541</v>
+        <v>0.05950713143373058</v>
       </c>
       <c r="AB2">
-        <v>0.06308169606357884</v>
+        <v>0.09599481073509882</v>
       </c>
       <c r="AC2">
-        <v>0.02935181549997656</v>
+        <v>-0.03648767930136824</v>
       </c>
       <c r="AD2">
-        <v>58.3</v>
+        <v>43.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>58.3</v>
+        <v>43.3</v>
       </c>
       <c r="AG2">
-        <v>-66.90000000000001</v>
+        <v>-18</v>
       </c>
       <c r="AH2">
-        <v>0.1160429936305732</v>
+        <v>0.09933470979582472</v>
       </c>
       <c r="AI2">
-        <v>0.07625899280575539</v>
+        <v>0.07174813587406793</v>
       </c>
       <c r="AJ2">
-        <v>-0.1773594909862142</v>
+        <v>-0.04805125467164976</v>
       </c>
       <c r="AK2">
-        <v>-0.1046457062412013</v>
+        <v>-0.03319808188860199</v>
       </c>
       <c r="AL2">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AM2">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AN2">
-        <v>0.844927536231884</v>
+        <v>0.8457031249999999</v>
       </c>
       <c r="AO2">
-        <v>32.37113402061856</v>
+        <v>24.80874316939891</v>
       </c>
       <c r="AP2">
-        <v>-0.9695652173913044</v>
+        <v>-0.3515625</v>
       </c>
       <c r="AQ2">
-        <v>32.37113402061856</v>
+        <v>24.80874316939891</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0277</v>
+        <v>0.026</v>
       </c>
       <c r="E3">
-        <v>0.128</v>
+        <v>0.119</v>
       </c>
       <c r="G3">
-        <v>0.09964349376114082</v>
+        <v>0.1363073110285006</v>
       </c>
       <c r="H3">
-        <v>0.09964349376114082</v>
+        <v>0.1363073110285006</v>
       </c>
       <c r="I3">
-        <v>0.1119429590017825</v>
+        <v>0.09376290788930194</v>
       </c>
       <c r="J3">
-        <v>0.09457546459443993</v>
+        <v>0.0783719490195993</v>
       </c>
       <c r="K3">
-        <v>55</v>
+        <v>47.5</v>
       </c>
       <c r="L3">
-        <v>0.09803921568627451</v>
+        <v>0.09809995869475424</v>
       </c>
       <c r="M3">
-        <v>0.324</v>
+        <v>0.142</v>
       </c>
       <c r="N3">
-        <v>0.0007295654131952262</v>
+        <v>0.0003616912888436067</v>
       </c>
       <c r="O3">
-        <v>0.005890909090909091</v>
+        <v>0.002989473684210526</v>
       </c>
       <c r="P3">
-        <v>0.324</v>
+        <v>0.142</v>
       </c>
       <c r="Q3">
-        <v>0.0007295654131952262</v>
+        <v>0.0003616912888436067</v>
       </c>
       <c r="R3">
-        <v>0.005890909090909091</v>
+        <v>0.002989473684210526</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>125.2</v>
+        <v>61.3</v>
       </c>
       <c r="V3">
-        <v>0.2819184868272911</v>
+        <v>0.1561385634233316</v>
       </c>
       <c r="W3">
-        <v>0.08853831294269156</v>
+        <v>0.06741413567981834</v>
       </c>
       <c r="X3">
-        <v>0.06656083271809668</v>
+        <v>0.1001974742983223</v>
       </c>
       <c r="Y3">
-        <v>0.02197748022459488</v>
+        <v>-0.03278333861850391</v>
       </c>
       <c r="Z3">
-        <v>0.9773519163763066</v>
+        <v>0.7592912027599186</v>
       </c>
       <c r="AA3">
-        <v>0.09243351156355541</v>
+        <v>0.05950713143373058</v>
       </c>
       <c r="AB3">
-        <v>0.06308169606357884</v>
+        <v>0.09599481073509882</v>
       </c>
       <c r="AC3">
-        <v>0.02935181549997656</v>
+        <v>-0.03648767930136824</v>
       </c>
       <c r="AD3">
-        <v>58.3</v>
+        <v>43.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>58.3</v>
+        <v>43.3</v>
       </c>
       <c r="AG3">
-        <v>-66.90000000000001</v>
+        <v>-18</v>
       </c>
       <c r="AH3">
-        <v>0.1160429936305732</v>
+        <v>0.09933470979582472</v>
       </c>
       <c r="AI3">
-        <v>0.07625899280575539</v>
+        <v>0.07174813587406793</v>
       </c>
       <c r="AJ3">
-        <v>-0.1773594909862142</v>
+        <v>-0.04805125467164976</v>
       </c>
       <c r="AK3">
-        <v>-0.1046457062412013</v>
+        <v>-0.03319808188860199</v>
       </c>
       <c r="AL3">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AM3">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AN3">
-        <v>0.844927536231884</v>
+        <v>0.8457031249999999</v>
       </c>
       <c r="AO3">
-        <v>32.37113402061856</v>
+        <v>24.80874316939891</v>
       </c>
       <c r="AP3">
-        <v>-0.9695652173913044</v>
+        <v>-0.3515625</v>
       </c>
       <c r="AQ3">
-        <v>32.37113402061856</v>
+        <v>24.80874316939891</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/croatia/croatia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_insurance_general.xlsx
@@ -588,121 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.026</v>
+        <v>0.0377</v>
       </c>
       <c r="E2">
-        <v>0.119</v>
+        <v>-0.0537</v>
       </c>
       <c r="G2">
-        <v>0.1363073110285006</v>
+        <v>0.122650840751731</v>
       </c>
       <c r="H2">
-        <v>0.1363073110285006</v>
+        <v>0.122650840751731</v>
       </c>
       <c r="I2">
-        <v>0.09376290788930194</v>
+        <v>0.08902077151335311</v>
       </c>
       <c r="J2">
-        <v>0.0783719490195993</v>
+        <v>0.07677555621784821</v>
       </c>
       <c r="K2">
-        <v>47.5</v>
+        <v>39.4</v>
       </c>
       <c r="L2">
-        <v>0.09809995869475424</v>
+        <v>0.06495219254863172</v>
       </c>
       <c r="M2">
-        <v>0.142</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0003616912888436067</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.002989473684210526</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.142</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0003616912888436067</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.002989473684210526</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>61.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V2">
-        <v>0.1561385634233316</v>
+        <v>0.2096894409937888</v>
       </c>
       <c r="W2">
-        <v>0.06741413567981834</v>
+        <v>0.07050823192555476</v>
       </c>
       <c r="X2">
-        <v>0.1001974742983223</v>
+        <v>0.08932824809990358</v>
       </c>
       <c r="Y2">
-        <v>-0.03278333861850391</v>
+        <v>-0.01882001617434882</v>
       </c>
       <c r="Z2">
-        <v>0.7592912027599186</v>
+        <v>1.121671597633136</v>
       </c>
       <c r="AA2">
-        <v>0.05950713143373058</v>
+        <v>0.08611696080204646</v>
       </c>
       <c r="AB2">
-        <v>0.09599481073509882</v>
+        <v>0.08550914771795572</v>
       </c>
       <c r="AC2">
-        <v>-0.03648767930136824</v>
+        <v>0.000607813084090747</v>
       </c>
       <c r="AD2">
-        <v>43.3</v>
+        <v>48.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>43.3</v>
+        <v>48.7</v>
       </c>
       <c r="AG2">
-        <v>-18</v>
+        <v>-35.7</v>
       </c>
       <c r="AH2">
-        <v>0.09933470979582472</v>
+        <v>0.1079343971631206</v>
       </c>
       <c r="AI2">
-        <v>0.07174813587406793</v>
+        <v>0.05990159901599016</v>
       </c>
       <c r="AJ2">
-        <v>-0.04805125467164976</v>
+        <v>-0.09732824427480917</v>
       </c>
       <c r="AK2">
-        <v>-0.03319808188860199</v>
+        <v>-0.04899807850672524</v>
       </c>
       <c r="AL2">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AM2">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AN2">
-        <v>0.8457031249999999</v>
+        <v>0.7957516339869282</v>
       </c>
       <c r="AO2">
-        <v>24.80874316939891</v>
+        <v>28.27225130890053</v>
       </c>
       <c r="AP2">
-        <v>-0.3515625</v>
+        <v>-0.5833333333333334</v>
       </c>
       <c r="AQ2">
-        <v>24.80874316939891</v>
+        <v>28.27225130890053</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.026</v>
+        <v>0.0377</v>
       </c>
       <c r="E3">
-        <v>0.119</v>
+        <v>-0.0537</v>
       </c>
       <c r="G3">
-        <v>0.1363073110285006</v>
+        <v>0.122650840751731</v>
       </c>
       <c r="H3">
-        <v>0.1363073110285006</v>
+        <v>0.122650840751731</v>
       </c>
       <c r="I3">
-        <v>0.09376290788930194</v>
+        <v>0.08902077151335311</v>
       </c>
       <c r="J3">
-        <v>0.0783719490195993</v>
+        <v>0.07677555621784821</v>
       </c>
       <c r="K3">
-        <v>47.5</v>
+        <v>39.4</v>
       </c>
       <c r="L3">
-        <v>0.09809995869475424</v>
+        <v>0.06495219254863172</v>
       </c>
       <c r="M3">
-        <v>0.142</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0003616912888436067</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.002989473684210526</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.142</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0003616912888436067</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.002989473684210526</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>61.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V3">
-        <v>0.1561385634233316</v>
+        <v>0.2096894409937888</v>
       </c>
       <c r="W3">
-        <v>0.06741413567981834</v>
+        <v>0.07050823192555476</v>
       </c>
       <c r="X3">
-        <v>0.1001974742983223</v>
+        <v>0.08932824809990358</v>
       </c>
       <c r="Y3">
-        <v>-0.03278333861850391</v>
+        <v>-0.01882001617434882</v>
       </c>
       <c r="Z3">
-        <v>0.7592912027599186</v>
+        <v>1.121671597633136</v>
       </c>
       <c r="AA3">
-        <v>0.05950713143373058</v>
+        <v>0.08611696080204646</v>
       </c>
       <c r="AB3">
-        <v>0.09599481073509882</v>
+        <v>0.08550914771795572</v>
       </c>
       <c r="AC3">
-        <v>-0.03648767930136824</v>
+        <v>0.000607813084090747</v>
       </c>
       <c r="AD3">
-        <v>43.3</v>
+        <v>48.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>43.3</v>
+        <v>48.7</v>
       </c>
       <c r="AG3">
-        <v>-18</v>
+        <v>-35.7</v>
       </c>
       <c r="AH3">
-        <v>0.09933470979582472</v>
+        <v>0.1079343971631206</v>
       </c>
       <c r="AI3">
-        <v>0.07174813587406793</v>
+        <v>0.05990159901599016</v>
       </c>
       <c r="AJ3">
-        <v>-0.04805125467164976</v>
+        <v>-0.09732824427480917</v>
       </c>
       <c r="AK3">
-        <v>-0.03319808188860199</v>
+        <v>-0.04899807850672524</v>
       </c>
       <c r="AL3">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AM3">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AN3">
-        <v>0.8457031249999999</v>
+        <v>0.7957516339869282</v>
       </c>
       <c r="AO3">
-        <v>24.80874316939891</v>
+        <v>28.27225130890053</v>
       </c>
       <c r="AP3">
-        <v>-0.3515625</v>
+        <v>-0.5833333333333334</v>
       </c>
       <c r="AQ3">
-        <v>24.80874316939891</v>
+        <v>28.27225130890053</v>
       </c>
     </row>
   </sheetData>
